--- a/Req_Handoff_Check.xlsx
+++ b/Req_Handoff_Check.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sampath.sho\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDC0CA0B-60A0-4F39-B122-D873C815F996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1EE94B7-EFD9-452D-9667-4D9D6F2EBF99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="5" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="9" r:id="rId1"/>
@@ -122,7 +122,7 @@
     <t>• 1 job was opened in iCIMS before its request was approved.</t>
   </si>
   <si>
-    <t>• 5 approved requests are stale gaps: approved over a week ago and still not in iCIMS.</t>
+    <t>• 5 requests flag as stale gaps, but only 3 are real: one sits in iCIMS under the typo'd ID, one is a duplicate.</t>
   </si>
   <si>
     <t>• Smaller cleanup: 1 duplicate request pair, 3 dates stored as text and 3 missing locations.</t>
@@ -20067,7 +20067,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" customWidth="1"/>
     <col min="3" max="3" width="16.42578125" customWidth="1"/>
     <col min="4" max="4" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
